--- a/output/第10期計画_町別データシート.xlsx
+++ b/output/第10期計画_町別データシート.xlsx
@@ -1964,7 +1964,7 @@
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>令和7年度は、3町のファイルの合計（3,213,054,558円）と広域連合単位のファイルの値（3,083,474,291円）に129,580,267円の差があります。令和6年度・令和8年度は一致します。差は要介護度により1.7％から5.9％まで幅があり、月数の違いによる一様な差ではありません。確認事項No.87として管理しています。</t>
+          <t>3町のファイルの合計と広域連合単位のファイルの値は、令和6年度から令和8年度まで要介護度ごとに円単位で一致します。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>令和7年度は、3町のファイルの合計（3,213,054,558円）と広域連合単位のファイルの値（3,083,474,291円）に129,580,267円の差があります。令和6年度・令和8年度は一致します。差は要介護度により1.7％から5.9％まで幅があり、月数の違いによる一様な差ではありません。確認事項No.87として管理しています。</t>
+          <t>3町のファイルの合計と広域連合単位のファイルの値は、令和6年度から令和8年度まで要介護度ごとに円単位で一致します。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>令和7年度は、3町のファイルの合計（3,213,054,558円）と広域連合単位のファイルの値（3,083,474,291円）に129,580,267円の差があります。令和6年度・令和8年度は一致します。差は要介護度により1.7％から5.9％まで幅があり、月数の違いによる一様な差ではありません。確認事項No.87として管理しています。</t>
+          <t>3町のファイルの合計と広域連合単位のファイルの値は、令和6年度から令和8年度まで要介護度ごとに円単位で一致します。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_町別データシート.xlsx
+++ b/output/第10期計画_町別データシート.xlsx
@@ -2197,7 +2197,7 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。</t>
+          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。また本表は計画作成支援ツール（3町がそれぞれ入力した値）によるものであり、3町を足しても介護保険事業状況報告年報による保険者単位の値にはなりません（確認事項No.145）。サービス見込量・給付費・保険料は年報による保険者単位の値で算定しています。</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。</t>
+          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。また本表は計画作成支援ツール（3町がそれぞれ入力した値）によるものであり、3町を足しても介護保険事業状況報告年報による保険者単位の値にはなりません（確認事項No.145）。サービス見込量・給付費・保険料は年報による保険者単位の値で算定しています。</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。</t>
+          <t>本表は町の被保険者が利用した月平均の人数であり、町内に所在する施設の定員ではありません。町外の施設を利用した分を含み、町内の施設を町外の被保険者が利用した分を含みません。施設の定員は計画素案 第2章第3節6に広域連合の値として掲げています。また本表は計画作成支援ツール（3町がそれぞれ入力した値）によるものであり、3町を足しても介護保険事業状況報告年報による保険者単位の値にはなりません（確認事項No.145）。サービス見込量・給付費・保険料は年報による保険者単位の値で算定しています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_町別データシート.xlsx
+++ b/output/第10期計画_町別データシート.xlsx
@@ -9692,7 +9692,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本表の数値と記述を、出典から独立に再計算して突き合わせた結果です。点検は build_town_datasheet_review.py により機械的に行い、指摘が0件になるまで作成と点検を繰り返しています。点検日：令和8年9月9日。</t>
+          <t>本表の数値と記述を、出典から独立に再計算して突き合わせた結果です。点検は機械的に行い、指摘が0件になるまで作成と点検を繰り返しています。点検日：令和8年9月9日。</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>注1）点検は build_town_datasheet_review.py によります。同スクリプトは出典のデータモジュール（住民基本台帳・計画作成支援ツール・給付費データ集計・交付金の公表資料）及び他の成果品の実物から独立に再計算し、本表の値と突き合わせます。指摘が1件でも残る場合は終了コード1で終わります。</t>
+          <t>注1）点検は、出典のデータ（住民基本台帳・計画作成支援ツール・給付費データ集計・交付金の公表資料）及び他の成果品から独立に再計算し、本表の値と突き合わせます。指摘が1件でも残る場合は作成を止めます。</t>
         </is>
       </c>
     </row>
